--- a/lexicon/sanskrit-monier-williams/sql-matching/skt-lex-ref-link-demotions.xlsx
+++ b/lexicon/sanskrit-monier-williams/sql-matching/skt-lex-ref-link-demotions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jayb3\Source\Repos\uky\derbi-pie-dev\MySQL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jayb3\Source\Repos\uky\derbi-pie-dev\lexicon\sanskrit-monier-williams\sql-matching\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83616E8-58A1-46E8-A79B-BF4529703C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7151DEE0-44E8-4177-B4F5-39638B2C50FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{40E2B794-21D7-41E0-B60E-36B49EE51F68}"/>
   </bookViews>
@@ -1726,11 +1726,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1783,6 +1784,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6FF7D5B7-748C-4A0C-B4F0-1C74E68C4EA6}" name="skt_lex_ref_link_demoted" displayName="skt_lex_ref_link_demoted" ref="A1:G151" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G151" xr:uid="{6FF7D5B7-748C-4A0C-B4F0-1C74E68C4EA6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:G149">
+    <sortCondition ref="G1:G151"/>
+  </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{65D6C6E4-620A-4EE8-8869-64F5F7A3BD2D}" uniqueName="1" name="lex_ref_link_id" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{6BE504C3-9E14-474B-A4E8-4A7849049029}" uniqueName="2" name="orig_word_id" queryTableFieldId="2"/>
@@ -2155,19 +2159,19 @@
       <c r="B2">
         <v>7280</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2">
         <v>7278</v>
       </c>
     </row>
@@ -2178,19 +2182,19 @@
       <c r="B3">
         <v>41188</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>41186</v>
       </c>
     </row>
@@ -2201,19 +2205,19 @@
       <c r="B4">
         <v>46424</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>46418</v>
       </c>
     </row>
@@ -2224,158 +2228,158 @@
       <c r="B5">
         <v>80244</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>80243</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>56348</v>
+        <v>81137</v>
       </c>
       <c r="B6">
-        <v>119573</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>300561</v>
+      </c>
+      <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>216</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>56349</v>
+        <v>20462</v>
       </c>
       <c r="B7">
-        <v>119573</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>461</v>
+        <v>300006</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>56350</v>
+        <v>33975</v>
       </c>
       <c r="B8">
-        <v>119573</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>461</v>
+        <v>300031</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>56351</v>
+        <v>35515</v>
       </c>
       <c r="B9">
-        <v>119573</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>461</v>
+        <v>300032</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>84335</v>
+        <v>21200</v>
       </c>
       <c r="B10">
-        <v>143453</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>300044</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>84343</v>
+        <v>21106</v>
       </c>
       <c r="B11">
-        <v>143453</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>300061</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" t="s">
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2385,19 +2389,19 @@
       <c r="B12">
         <v>151564</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>151562</v>
       </c>
     </row>
@@ -2408,66 +2412,66 @@
       <c r="B13">
         <v>195347</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>195346</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>41246</v>
+        <v>35937</v>
       </c>
       <c r="B14">
-        <v>200935</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>459</v>
+        <v>300061</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>45162</v>
+        <v>20454</v>
       </c>
       <c r="B15">
-        <v>202861</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>462</v>
+        <v>300150</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2477,19 +2481,19 @@
       <c r="B16">
         <v>300002</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16">
         <v>301312</v>
       </c>
     </row>
@@ -2500,112 +2504,112 @@
       <c r="B17">
         <v>300002</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17">
         <v>301312</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>20462</v>
+        <v>28302</v>
       </c>
       <c r="B18">
-        <v>300006</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>463</v>
+        <v>300150</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>33975</v>
+        <v>61081</v>
       </c>
       <c r="B19">
-        <v>300031</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>464</v>
+        <v>300161</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>35515</v>
+        <v>61082</v>
       </c>
       <c r="B20">
-        <v>300032</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>465</v>
+        <v>300161</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>21200</v>
+        <v>37202</v>
       </c>
       <c r="B21">
-        <v>300044</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>466</v>
+        <v>300163</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2615,66 +2619,66 @@
       <c r="B22">
         <v>300060</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22">
         <v>7511</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21106</v>
+        <v>33736</v>
       </c>
       <c r="B23">
-        <v>300061</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>467</v>
+        <v>300171</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>35937</v>
+        <v>37159</v>
       </c>
       <c r="B24">
-        <v>300061</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>467</v>
+        <v>300215</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2684,19 +2688,19 @@
       <c r="B25">
         <v>300111</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25">
         <v>302535</v>
       </c>
     </row>
@@ -2707,19 +2711,19 @@
       <c r="B26">
         <v>300111</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26">
         <v>302535</v>
       </c>
     </row>
@@ -2730,480 +2734,480 @@
       <c r="B27">
         <v>300111</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27">
         <v>302535</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>20454</v>
+        <v>37162</v>
       </c>
       <c r="B28">
-        <v>300150</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>468</v>
+        <v>300215</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28302</v>
+        <v>61833</v>
       </c>
       <c r="B29">
-        <v>300150</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>468</v>
+        <v>300217</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>61081</v>
+        <v>34524</v>
       </c>
       <c r="B30">
-        <v>300161</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>469</v>
+        <v>300226</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>61082</v>
+        <v>34527</v>
       </c>
       <c r="B31">
-        <v>300161</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>469</v>
+        <v>300226</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>37202</v>
+        <v>34541</v>
       </c>
       <c r="B32">
-        <v>300163</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>470</v>
+        <v>300226</v>
+      </c>
+      <c r="C32" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>33736</v>
+        <v>34595</v>
       </c>
       <c r="B33">
-        <v>300171</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>471</v>
+        <v>300226</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>37159</v>
+        <v>22651</v>
       </c>
       <c r="B34">
-        <v>300215</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>472</v>
+        <v>300244</v>
+      </c>
+      <c r="C34" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>37162</v>
+        <v>22657</v>
       </c>
       <c r="B35">
-        <v>300215</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>472</v>
+        <v>300248</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>61833</v>
+        <v>36279</v>
       </c>
       <c r="B36">
-        <v>300217</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>473</v>
+        <v>300308</v>
+      </c>
+      <c r="C36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G36" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>34524</v>
+        <v>36282</v>
       </c>
       <c r="B37">
-        <v>300226</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>474</v>
+        <v>300308</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" t="s">
+        <v>132</v>
+      </c>
+      <c r="F37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>34527</v>
+        <v>36286</v>
       </c>
       <c r="B38">
-        <v>300226</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>474</v>
+        <v>300308</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>34541</v>
+        <v>36287</v>
       </c>
       <c r="B39">
-        <v>300226</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>474</v>
+        <v>300308</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G39" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>34595</v>
+        <v>36296</v>
       </c>
       <c r="B40">
-        <v>300226</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>474</v>
+        <v>300308</v>
+      </c>
+      <c r="C40" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" t="s">
+        <v>133</v>
+      </c>
+      <c r="G40" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>22651</v>
+        <v>3856</v>
       </c>
       <c r="B41">
-        <v>300244</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>475</v>
+        <v>300361</v>
+      </c>
+      <c r="C41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" t="s">
+        <v>154</v>
+      </c>
+      <c r="G41" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>22657</v>
+        <v>3920</v>
       </c>
       <c r="B42">
-        <v>300248</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>476</v>
+        <v>300361</v>
+      </c>
+      <c r="C42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>36279</v>
+        <v>46259</v>
       </c>
       <c r="B43">
-        <v>300308</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>477</v>
+        <v>300370</v>
+      </c>
+      <c r="C43" t="s">
+        <v>155</v>
+      </c>
+      <c r="D43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" t="s">
+        <v>157</v>
+      </c>
+      <c r="F43" t="s">
+        <v>158</v>
+      </c>
+      <c r="G43" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>36282</v>
+        <v>46261</v>
       </c>
       <c r="B44">
-        <v>300308</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>477</v>
+        <v>300370</v>
+      </c>
+      <c r="C44" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" t="s">
+        <v>157</v>
+      </c>
+      <c r="F44" t="s">
+        <v>158</v>
+      </c>
+      <c r="G44" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>36286</v>
+        <v>52778</v>
       </c>
       <c r="B45">
-        <v>300308</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>477</v>
+        <v>300374</v>
+      </c>
+      <c r="C45" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45" t="s">
+        <v>163</v>
+      </c>
+      <c r="F45" t="s">
+        <v>164</v>
+      </c>
+      <c r="G45" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>36287</v>
+        <v>53431</v>
       </c>
       <c r="B46">
-        <v>300308</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>477</v>
+        <v>300410</v>
+      </c>
+      <c r="C46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" t="s">
+        <v>167</v>
+      </c>
+      <c r="F46" t="s">
+        <v>168</v>
+      </c>
+      <c r="G46" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>36296</v>
+        <v>45063</v>
       </c>
       <c r="B47">
-        <v>300308</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>477</v>
+        <v>300435</v>
+      </c>
+      <c r="C47" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G47" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3213,19 +3217,19 @@
       <c r="B48">
         <v>300329</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>141</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>142</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" t="s">
         <v>143</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>144</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G48">
         <v>32495</v>
       </c>
     </row>
@@ -3236,19 +3240,19 @@
       <c r="B49">
         <v>300329</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>145</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>146</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" t="s">
         <v>143</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" t="s">
         <v>144</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G49">
         <v>32495</v>
       </c>
     </row>
@@ -3259,457 +3263,457 @@
       <c r="B50">
         <v>300332</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>147</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>148</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" t="s">
         <v>149</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" t="s">
         <v>150</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50">
         <v>305454</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>3856</v>
+        <v>40454</v>
       </c>
       <c r="B51">
-        <v>300361</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>478</v>
+        <v>300464</v>
+      </c>
+      <c r="C51" t="s">
+        <v>173</v>
+      </c>
+      <c r="D51" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" t="s">
+        <v>175</v>
+      </c>
+      <c r="F51" t="s">
+        <v>176</v>
+      </c>
+      <c r="G51" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>3920</v>
+        <v>40455</v>
       </c>
       <c r="B52">
-        <v>300361</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>478</v>
+        <v>300464</v>
+      </c>
+      <c r="C52" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>46259</v>
+        <v>44926</v>
       </c>
       <c r="B53">
-        <v>300370</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>479</v>
+        <v>300465</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" t="s">
+        <v>175</v>
+      </c>
+      <c r="F53" t="s">
+        <v>181</v>
+      </c>
+      <c r="G53" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>46261</v>
+        <v>44386</v>
       </c>
       <c r="B54">
-        <v>300370</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>479</v>
+        <v>300470</v>
+      </c>
+      <c r="C54" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" t="s">
+        <v>183</v>
+      </c>
+      <c r="E54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F54" t="s">
+        <v>185</v>
+      </c>
+      <c r="G54" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>52778</v>
+        <v>44387</v>
       </c>
       <c r="B55">
-        <v>300374</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>480</v>
+        <v>300470</v>
+      </c>
+      <c r="C55" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" t="s">
+        <v>185</v>
+      </c>
+      <c r="G55" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>53431</v>
+        <v>44388</v>
       </c>
       <c r="B56">
-        <v>300410</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>481</v>
+        <v>300470</v>
+      </c>
+      <c r="C56" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" t="s">
+        <v>184</v>
+      </c>
+      <c r="F56" t="s">
+        <v>185</v>
+      </c>
+      <c r="G56" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>45063</v>
+        <v>44389</v>
       </c>
       <c r="B57">
-        <v>300435</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>482</v>
+        <v>300470</v>
+      </c>
+      <c r="C57" t="s">
+        <v>188</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>184</v>
+      </c>
+      <c r="F57" t="s">
+        <v>185</v>
+      </c>
+      <c r="G57" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>40454</v>
+        <v>46295</v>
       </c>
       <c r="B58">
-        <v>300464</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>483</v>
+        <v>300489</v>
+      </c>
+      <c r="C58" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" t="s">
+        <v>190</v>
+      </c>
+      <c r="E58" t="s">
+        <v>191</v>
+      </c>
+      <c r="F58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G58" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>40455</v>
+        <v>43196</v>
       </c>
       <c r="B59">
-        <v>300464</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>483</v>
+        <v>300511</v>
+      </c>
+      <c r="C59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" t="s">
+        <v>194</v>
+      </c>
+      <c r="E59" t="s">
+        <v>195</v>
+      </c>
+      <c r="F59" t="s">
+        <v>196</v>
+      </c>
+      <c r="G59" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>44926</v>
+        <v>39363</v>
       </c>
       <c r="B60">
-        <v>300465</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>484</v>
+        <v>300528</v>
+      </c>
+      <c r="C60" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" t="s">
+        <v>198</v>
+      </c>
+      <c r="E60" t="s">
+        <v>199</v>
+      </c>
+      <c r="F60" t="s">
+        <v>200</v>
+      </c>
+      <c r="G60" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>44386</v>
+        <v>79332</v>
       </c>
       <c r="B61">
-        <v>300470</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>485</v>
+        <v>300542</v>
+      </c>
+      <c r="C61" t="s">
+        <v>201</v>
+      </c>
+      <c r="D61" t="s">
+        <v>202</v>
+      </c>
+      <c r="E61" t="s">
+        <v>203</v>
+      </c>
+      <c r="F61" t="s">
+        <v>204</v>
+      </c>
+      <c r="G61" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>44387</v>
+        <v>76547</v>
       </c>
       <c r="B62">
-        <v>300470</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>485</v>
+        <v>300544</v>
+      </c>
+      <c r="C62" t="s">
+        <v>205</v>
+      </c>
+      <c r="D62" t="s">
+        <v>206</v>
+      </c>
+      <c r="E62" t="s">
+        <v>207</v>
+      </c>
+      <c r="F62" t="s">
+        <v>208</v>
+      </c>
+      <c r="G62" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>44388</v>
+        <v>81138</v>
       </c>
       <c r="B63">
-        <v>300470</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>485</v>
+        <v>300561</v>
+      </c>
+      <c r="C63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D63" t="s">
+        <v>214</v>
+      </c>
+      <c r="E63" t="s">
+        <v>215</v>
+      </c>
+      <c r="F63" t="s">
+        <v>216</v>
+      </c>
+      <c r="G63" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>44389</v>
+        <v>80987</v>
       </c>
       <c r="B64">
-        <v>300470</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>485</v>
+        <v>300573</v>
+      </c>
+      <c r="C64" t="s">
+        <v>218</v>
+      </c>
+      <c r="D64" t="s">
+        <v>219</v>
+      </c>
+      <c r="E64" t="s">
+        <v>220</v>
+      </c>
+      <c r="F64" t="s">
+        <v>221</v>
+      </c>
+      <c r="G64" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>46295</v>
+        <v>30660</v>
       </c>
       <c r="B65">
-        <v>300489</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>486</v>
+        <v>300582</v>
+      </c>
+      <c r="C65" t="s">
+        <v>222</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>223</v>
+      </c>
+      <c r="F65" t="s">
+        <v>224</v>
+      </c>
+      <c r="G65" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>43196</v>
+        <v>28663</v>
       </c>
       <c r="B66">
-        <v>300511</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>487</v>
+        <v>300599</v>
+      </c>
+      <c r="C66" t="s">
+        <v>225</v>
+      </c>
+      <c r="D66" t="s">
+        <v>226</v>
+      </c>
+      <c r="E66" t="s">
+        <v>227</v>
+      </c>
+      <c r="F66" t="s">
+        <v>228</v>
+      </c>
+      <c r="G66" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>39363</v>
+        <v>28527</v>
       </c>
       <c r="B67">
-        <v>300528</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>488</v>
+        <v>300602</v>
+      </c>
+      <c r="C67" t="s">
+        <v>229</v>
+      </c>
+      <c r="D67" t="s">
+        <v>230</v>
+      </c>
+      <c r="E67" t="s">
+        <v>231</v>
+      </c>
+      <c r="F67" t="s">
+        <v>232</v>
+      </c>
+      <c r="G67" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>79332</v>
+        <v>28528</v>
       </c>
       <c r="B68">
-        <v>300542</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>489</v>
+        <v>300602</v>
+      </c>
+      <c r="C68" t="s">
+        <v>233</v>
+      </c>
+      <c r="D68" t="s">
+        <v>230</v>
+      </c>
+      <c r="E68" t="s">
+        <v>231</v>
+      </c>
+      <c r="F68" t="s">
+        <v>232</v>
+      </c>
+      <c r="G68" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>76547</v>
+        <v>28529</v>
       </c>
       <c r="B69">
-        <v>300544</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>490</v>
+        <v>300602</v>
+      </c>
+      <c r="C69" t="s">
+        <v>234</v>
+      </c>
+      <c r="D69" t="s">
+        <v>230</v>
+      </c>
+      <c r="E69" t="s">
+        <v>231</v>
+      </c>
+      <c r="F69" t="s">
+        <v>232</v>
+      </c>
+      <c r="G69" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3719,687 +3723,687 @@
       <c r="B70">
         <v>300548</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>209</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" t="s">
         <v>210</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" t="s">
         <v>211</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" t="s">
         <v>212</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70">
         <v>63270</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>81137</v>
+        <v>28530</v>
       </c>
       <c r="B71">
-        <v>300561</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>491</v>
+        <v>300602</v>
+      </c>
+      <c r="C71" t="s">
+        <v>235</v>
+      </c>
+      <c r="D71" t="s">
+        <v>230</v>
+      </c>
+      <c r="E71" t="s">
+        <v>231</v>
+      </c>
+      <c r="F71" t="s">
+        <v>232</v>
+      </c>
+      <c r="G71" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>81138</v>
+        <v>33333</v>
       </c>
       <c r="B72">
-        <v>300561</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>492</v>
+        <v>300610</v>
+      </c>
+      <c r="C72" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" t="s">
+        <v>237</v>
+      </c>
+      <c r="E72" t="s">
+        <v>238</v>
+      </c>
+      <c r="F72" t="s">
+        <v>239</v>
+      </c>
+      <c r="G72" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>80987</v>
+        <v>33334</v>
       </c>
       <c r="B73">
-        <v>300573</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>493</v>
+        <v>300610</v>
+      </c>
+      <c r="C73" t="s">
+        <v>240</v>
+      </c>
+      <c r="D73" t="s">
+        <v>241</v>
+      </c>
+      <c r="E73" t="s">
+        <v>238</v>
+      </c>
+      <c r="F73" t="s">
+        <v>239</v>
+      </c>
+      <c r="G73" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>30660</v>
+        <v>30016</v>
       </c>
       <c r="B74">
-        <v>300582</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>494</v>
+        <v>300615</v>
+      </c>
+      <c r="C74" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" t="s">
+        <v>243</v>
+      </c>
+      <c r="E74" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" t="s">
+        <v>245</v>
+      </c>
+      <c r="G74" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>28663</v>
+        <v>29642</v>
       </c>
       <c r="B75">
-        <v>300599</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>495</v>
+        <v>300625</v>
+      </c>
+      <c r="C75" t="s">
+        <v>246</v>
+      </c>
+      <c r="D75" t="s">
+        <v>247</v>
+      </c>
+      <c r="E75" t="s">
+        <v>248</v>
+      </c>
+      <c r="F75" t="s">
+        <v>249</v>
+      </c>
+      <c r="G75" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>28527</v>
+        <v>32110</v>
       </c>
       <c r="B76">
-        <v>300602</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>496</v>
+        <v>300632</v>
+      </c>
+      <c r="C76" t="s">
+        <v>250</v>
+      </c>
+      <c r="D76" t="s">
+        <v>251</v>
+      </c>
+      <c r="E76" t="s">
+        <v>252</v>
+      </c>
+      <c r="F76" t="s">
+        <v>253</v>
+      </c>
+      <c r="G76" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>28528</v>
+        <v>33056</v>
       </c>
       <c r="B77">
-        <v>300602</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>496</v>
+        <v>300659</v>
+      </c>
+      <c r="C77" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" t="s">
+        <v>255</v>
+      </c>
+      <c r="E77" t="s">
+        <v>256</v>
+      </c>
+      <c r="F77" t="s">
+        <v>257</v>
+      </c>
+      <c r="G77" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>28529</v>
+        <v>60774</v>
       </c>
       <c r="B78">
-        <v>300602</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>496</v>
+        <v>300669</v>
+      </c>
+      <c r="C78" t="s">
+        <v>258</v>
+      </c>
+      <c r="D78" t="s">
+        <v>259</v>
+      </c>
+      <c r="E78" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" t="s">
+        <v>260</v>
+      </c>
+      <c r="G78" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>28530</v>
+        <v>60487</v>
       </c>
       <c r="B79">
-        <v>300602</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>496</v>
+        <v>300674</v>
+      </c>
+      <c r="C79" t="s">
+        <v>261</v>
+      </c>
+      <c r="D79" t="s">
+        <v>262</v>
+      </c>
+      <c r="E79" t="s">
+        <v>263</v>
+      </c>
+      <c r="F79" t="s">
+        <v>264</v>
+      </c>
+      <c r="G79" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>33333</v>
+        <v>60838</v>
       </c>
       <c r="B80">
-        <v>300610</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>497</v>
+        <v>300696</v>
+      </c>
+      <c r="C80" t="s">
+        <v>265</v>
+      </c>
+      <c r="D80" t="s">
+        <v>266</v>
+      </c>
+      <c r="E80" t="s">
+        <v>267</v>
+      </c>
+      <c r="F80" t="s">
+        <v>268</v>
+      </c>
+      <c r="G80" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>33334</v>
+        <v>60839</v>
       </c>
       <c r="B81">
-        <v>300610</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>497</v>
+        <v>300696</v>
+      </c>
+      <c r="C81" t="s">
+        <v>269</v>
+      </c>
+      <c r="D81" t="s">
+        <v>266</v>
+      </c>
+      <c r="E81" t="s">
+        <v>267</v>
+      </c>
+      <c r="F81" t="s">
+        <v>268</v>
+      </c>
+      <c r="G81" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>30016</v>
+        <v>60840</v>
       </c>
       <c r="B82">
-        <v>300615</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>498</v>
+        <v>300696</v>
+      </c>
+      <c r="C82" t="s">
+        <v>270</v>
+      </c>
+      <c r="D82" t="s">
+        <v>271</v>
+      </c>
+      <c r="E82" t="s">
+        <v>267</v>
+      </c>
+      <c r="F82" t="s">
+        <v>268</v>
+      </c>
+      <c r="G82" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>29642</v>
+        <v>60421</v>
       </c>
       <c r="B83">
-        <v>300625</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>499</v>
+        <v>300700</v>
+      </c>
+      <c r="C83" t="s">
+        <v>272</v>
+      </c>
+      <c r="D83" t="s">
+        <v>273</v>
+      </c>
+      <c r="E83" t="s">
+        <v>274</v>
+      </c>
+      <c r="F83" t="s">
+        <v>275</v>
+      </c>
+      <c r="G83" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>32110</v>
+        <v>60086</v>
       </c>
       <c r="B84">
-        <v>300632</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>500</v>
+        <v>300701</v>
+      </c>
+      <c r="C84" t="s">
+        <v>276</v>
+      </c>
+      <c r="D84" t="s">
+        <v>277</v>
+      </c>
+      <c r="E84" t="s">
+        <v>278</v>
+      </c>
+      <c r="F84" t="s">
+        <v>279</v>
+      </c>
+      <c r="G84" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>33056</v>
+        <v>64358</v>
       </c>
       <c r="B85">
-        <v>300659</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>501</v>
+        <v>300709</v>
+      </c>
+      <c r="C85" t="s">
+        <v>280</v>
+      </c>
+      <c r="D85" t="s">
+        <v>281</v>
+      </c>
+      <c r="E85" t="s">
+        <v>282</v>
+      </c>
+      <c r="F85" t="s">
+        <v>283</v>
+      </c>
+      <c r="G85" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>60774</v>
+        <v>64359</v>
       </c>
       <c r="B86">
-        <v>300669</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>502</v>
+        <v>300709</v>
+      </c>
+      <c r="C86" t="s">
+        <v>284</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>282</v>
+      </c>
+      <c r="F86" t="s">
+        <v>283</v>
+      </c>
+      <c r="G86" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>60487</v>
+        <v>64360</v>
       </c>
       <c r="B87">
-        <v>300674</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>503</v>
+        <v>300709</v>
+      </c>
+      <c r="C87" t="s">
+        <v>285</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>282</v>
+      </c>
+      <c r="F87" t="s">
+        <v>283</v>
+      </c>
+      <c r="G87" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>60838</v>
+        <v>64361</v>
       </c>
       <c r="B88">
-        <v>300696</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>504</v>
+        <v>300709</v>
+      </c>
+      <c r="C88" t="s">
+        <v>286</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>282</v>
+      </c>
+      <c r="F88" t="s">
+        <v>283</v>
+      </c>
+      <c r="G88" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>60839</v>
+        <v>64362</v>
       </c>
       <c r="B89">
-        <v>300696</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>504</v>
+        <v>300709</v>
+      </c>
+      <c r="C89" t="s">
+        <v>287</v>
+      </c>
+      <c r="D89" t="s">
+        <v>288</v>
+      </c>
+      <c r="E89" t="s">
+        <v>282</v>
+      </c>
+      <c r="F89" t="s">
+        <v>283</v>
+      </c>
+      <c r="G89" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>60840</v>
+        <v>64363</v>
       </c>
       <c r="B90">
-        <v>300696</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>504</v>
+        <v>300709</v>
+      </c>
+      <c r="C90" t="s">
+        <v>289</v>
+      </c>
+      <c r="D90" t="s">
+        <v>290</v>
+      </c>
+      <c r="E90" t="s">
+        <v>282</v>
+      </c>
+      <c r="F90" t="s">
+        <v>283</v>
+      </c>
+      <c r="G90" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>60421</v>
+        <v>62167</v>
       </c>
       <c r="B91">
-        <v>300700</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>505</v>
+        <v>300711</v>
+      </c>
+      <c r="C91" t="s">
+        <v>291</v>
+      </c>
+      <c r="D91" t="s">
+        <v>292</v>
+      </c>
+      <c r="E91" t="s">
+        <v>293</v>
+      </c>
+      <c r="F91" t="s">
+        <v>294</v>
+      </c>
+      <c r="G91" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>60086</v>
+        <v>62097</v>
       </c>
       <c r="B92">
-        <v>300701</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>506</v>
+        <v>300752</v>
+      </c>
+      <c r="C92" t="s">
+        <v>299</v>
+      </c>
+      <c r="D92" t="s">
+        <v>300</v>
+      </c>
+      <c r="E92" t="s">
+        <v>301</v>
+      </c>
+      <c r="F92" t="s">
+        <v>302</v>
+      </c>
+      <c r="G92" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>64358</v>
+        <v>62098</v>
       </c>
       <c r="B93">
-        <v>300709</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>507</v>
+        <v>300752</v>
+      </c>
+      <c r="C93" t="s">
+        <v>303</v>
+      </c>
+      <c r="D93" t="s">
+        <v>300</v>
+      </c>
+      <c r="E93" t="s">
+        <v>301</v>
+      </c>
+      <c r="F93" t="s">
+        <v>302</v>
+      </c>
+      <c r="G93" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>64359</v>
+        <v>62099</v>
       </c>
       <c r="B94">
-        <v>300709</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>507</v>
+        <v>300752</v>
+      </c>
+      <c r="C94" t="s">
+        <v>304</v>
+      </c>
+      <c r="D94" t="s">
+        <v>300</v>
+      </c>
+      <c r="E94" t="s">
+        <v>301</v>
+      </c>
+      <c r="F94" t="s">
+        <v>302</v>
+      </c>
+      <c r="G94" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>64360</v>
+        <v>65784</v>
       </c>
       <c r="B95">
-        <v>300709</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>507</v>
+        <v>300752</v>
+      </c>
+      <c r="C95" t="s">
+        <v>305</v>
+      </c>
+      <c r="D95" t="s">
+        <v>306</v>
+      </c>
+      <c r="E95" t="s">
+        <v>301</v>
+      </c>
+      <c r="F95" t="s">
+        <v>302</v>
+      </c>
+      <c r="G95" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>64361</v>
+        <v>65785</v>
       </c>
       <c r="B96">
-        <v>300709</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>507</v>
+        <v>300752</v>
+      </c>
+      <c r="C96" t="s">
+        <v>303</v>
+      </c>
+      <c r="D96" t="s">
+        <v>306</v>
+      </c>
+      <c r="E96" t="s">
+        <v>301</v>
+      </c>
+      <c r="F96" t="s">
+        <v>302</v>
+      </c>
+      <c r="G96" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>64362</v>
+        <v>65786</v>
       </c>
       <c r="B97">
-        <v>300709</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>507</v>
+        <v>300752</v>
+      </c>
+      <c r="C97" t="s">
+        <v>307</v>
+      </c>
+      <c r="D97" t="s">
+        <v>306</v>
+      </c>
+      <c r="E97" t="s">
+        <v>301</v>
+      </c>
+      <c r="F97" t="s">
+        <v>302</v>
+      </c>
+      <c r="G97" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>64363</v>
+        <v>62708</v>
       </c>
       <c r="B98">
-        <v>300709</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>507</v>
+        <v>300754</v>
+      </c>
+      <c r="C98" t="s">
+        <v>308</v>
+      </c>
+      <c r="D98" t="s">
+        <v>309</v>
+      </c>
+      <c r="E98" t="s">
+        <v>310</v>
+      </c>
+      <c r="F98" t="s">
+        <v>311</v>
+      </c>
+      <c r="G98" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>62167</v>
+        <v>62298</v>
       </c>
       <c r="B99">
-        <v>300711</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>508</v>
+        <v>300758</v>
+      </c>
+      <c r="C99" t="s">
+        <v>312</v>
+      </c>
+      <c r="D99" t="s">
+        <v>313</v>
+      </c>
+      <c r="E99" t="s">
+        <v>314</v>
+      </c>
+      <c r="F99" t="s">
+        <v>315</v>
+      </c>
+      <c r="G99" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4409,503 +4413,503 @@
       <c r="B100">
         <v>300746</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" t="s">
         <v>295</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" t="s">
         <v>296</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" t="s">
         <v>297</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" t="s">
         <v>298</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G100">
         <v>96084</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>62097</v>
+        <v>64177</v>
       </c>
       <c r="B101">
-        <v>300752</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>509</v>
+        <v>300777</v>
+      </c>
+      <c r="C101" t="s">
+        <v>316</v>
+      </c>
+      <c r="D101" t="s">
+        <v>317</v>
+      </c>
+      <c r="E101" t="s">
+        <v>318</v>
+      </c>
+      <c r="F101" t="s">
+        <v>319</v>
+      </c>
+      <c r="G101" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>62098</v>
+        <v>56650</v>
       </c>
       <c r="B102">
-        <v>300752</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>509</v>
+        <v>300826</v>
+      </c>
+      <c r="C102" t="s">
+        <v>320</v>
+      </c>
+      <c r="D102" t="s">
+        <v>321</v>
+      </c>
+      <c r="E102" t="s">
+        <v>322</v>
+      </c>
+      <c r="F102" t="s">
+        <v>323</v>
+      </c>
+      <c r="G102" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>62099</v>
+        <v>56348</v>
       </c>
       <c r="B103">
-        <v>300752</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>509</v>
+        <v>119573</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" t="s">
+        <v>26</v>
+      </c>
+      <c r="F103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>65784</v>
+        <v>56349</v>
       </c>
       <c r="B104">
-        <v>300752</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>509</v>
+        <v>119573</v>
+      </c>
+      <c r="C104" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" t="s">
+        <v>26</v>
+      </c>
+      <c r="F104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G104" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>65785</v>
+        <v>56350</v>
       </c>
       <c r="B105">
-        <v>300752</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>509</v>
+        <v>119573</v>
+      </c>
+      <c r="C105" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" t="s">
+        <v>25</v>
+      </c>
+      <c r="E105" t="s">
+        <v>26</v>
+      </c>
+      <c r="F105" t="s">
+        <v>27</v>
+      </c>
+      <c r="G105" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>65786</v>
+        <v>56351</v>
       </c>
       <c r="B106">
-        <v>300752</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>509</v>
+        <v>119573</v>
+      </c>
+      <c r="C106" t="s">
+        <v>30</v>
+      </c>
+      <c r="D106" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" t="s">
+        <v>26</v>
+      </c>
+      <c r="F106" t="s">
+        <v>27</v>
+      </c>
+      <c r="G106" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>62708</v>
+        <v>58678</v>
       </c>
       <c r="B107">
-        <v>300754</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>510</v>
+        <v>300845</v>
+      </c>
+      <c r="C107" t="s">
+        <v>324</v>
+      </c>
+      <c r="D107" t="s">
+        <v>325</v>
+      </c>
+      <c r="E107" t="s">
+        <v>326</v>
+      </c>
+      <c r="F107" t="s">
+        <v>327</v>
+      </c>
+      <c r="G107" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>62298</v>
+        <v>59441</v>
       </c>
       <c r="B108">
-        <v>300758</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>511</v>
+        <v>300854</v>
+      </c>
+      <c r="C108" t="s">
+        <v>328</v>
+      </c>
+      <c r="D108" t="s">
+        <v>329</v>
+      </c>
+      <c r="E108" t="s">
+        <v>330</v>
+      </c>
+      <c r="F108" t="s">
+        <v>331</v>
+      </c>
+      <c r="G108" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>64177</v>
+        <v>59442</v>
       </c>
       <c r="B109">
-        <v>300777</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>512</v>
+        <v>300854</v>
+      </c>
+      <c r="C109" t="s">
+        <v>332</v>
+      </c>
+      <c r="D109" t="s">
+        <v>329</v>
+      </c>
+      <c r="E109" t="s">
+        <v>330</v>
+      </c>
+      <c r="F109" t="s">
+        <v>331</v>
+      </c>
+      <c r="G109" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>56650</v>
+        <v>59251</v>
       </c>
       <c r="B110">
-        <v>300826</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>513</v>
+        <v>300855</v>
+      </c>
+      <c r="C110" t="s">
+        <v>333</v>
+      </c>
+      <c r="D110" t="s">
+        <v>334</v>
+      </c>
+      <c r="E110" t="s">
+        <v>335</v>
+      </c>
+      <c r="F110" t="s">
+        <v>336</v>
+      </c>
+      <c r="G110" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>58678</v>
+        <v>59371</v>
       </c>
       <c r="B111">
-        <v>300845</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>514</v>
+        <v>300859</v>
+      </c>
+      <c r="C111" t="s">
+        <v>337</v>
+      </c>
+      <c r="D111" t="s">
+        <v>338</v>
+      </c>
+      <c r="E111" t="s">
+        <v>339</v>
+      </c>
+      <c r="F111" t="s">
+        <v>340</v>
+      </c>
+      <c r="G111" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>59441</v>
+        <v>59372</v>
       </c>
       <c r="B112">
-        <v>300854</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>515</v>
+        <v>300859</v>
+      </c>
+      <c r="C112" t="s">
+        <v>341</v>
+      </c>
+      <c r="D112" t="s">
+        <v>338</v>
+      </c>
+      <c r="E112" t="s">
+        <v>339</v>
+      </c>
+      <c r="F112" t="s">
+        <v>340</v>
+      </c>
+      <c r="G112" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>59442</v>
+        <v>59355</v>
       </c>
       <c r="B113">
-        <v>300854</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>515</v>
+        <v>300861</v>
+      </c>
+      <c r="C113" t="s">
+        <v>342</v>
+      </c>
+      <c r="D113" t="s">
+        <v>343</v>
+      </c>
+      <c r="E113" t="s">
+        <v>344</v>
+      </c>
+      <c r="F113" t="s">
+        <v>345</v>
+      </c>
+      <c r="G113" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>59251</v>
+        <v>33948</v>
       </c>
       <c r="B114">
-        <v>300855</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>516</v>
+        <v>300869</v>
+      </c>
+      <c r="C114" t="s">
+        <v>346</v>
+      </c>
+      <c r="D114" t="s">
+        <v>347</v>
+      </c>
+      <c r="E114" t="s">
+        <v>348</v>
+      </c>
+      <c r="F114" t="s">
+        <v>349</v>
+      </c>
+      <c r="G114" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>59371</v>
+        <v>33967</v>
       </c>
       <c r="B115">
-        <v>300859</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>517</v>
+        <v>300869</v>
+      </c>
+      <c r="C115" t="s">
+        <v>350</v>
+      </c>
+      <c r="D115" t="s">
+        <v>351</v>
+      </c>
+      <c r="E115" t="s">
+        <v>348</v>
+      </c>
+      <c r="F115" t="s">
+        <v>349</v>
+      </c>
+      <c r="G115" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>59372</v>
+        <v>45838</v>
       </c>
       <c r="B116">
-        <v>300859</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>517</v>
+        <v>300871</v>
+      </c>
+      <c r="C116" t="s">
+        <v>352</v>
+      </c>
+      <c r="D116" t="s">
+        <v>353</v>
+      </c>
+      <c r="E116" t="s">
+        <v>354</v>
+      </c>
+      <c r="F116" t="s">
+        <v>355</v>
+      </c>
+      <c r="G116" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>59355</v>
+        <v>45839</v>
       </c>
       <c r="B117">
-        <v>300861</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>518</v>
+        <v>300871</v>
+      </c>
+      <c r="C117" t="s">
+        <v>356</v>
+      </c>
+      <c r="D117" t="s">
+        <v>357</v>
+      </c>
+      <c r="E117" t="s">
+        <v>354</v>
+      </c>
+      <c r="F117" t="s">
+        <v>355</v>
+      </c>
+      <c r="G117" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>33948</v>
+        <v>66464</v>
       </c>
       <c r="B118">
-        <v>300869</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>519</v>
+        <v>300923</v>
+      </c>
+      <c r="C118" t="s">
+        <v>362</v>
+      </c>
+      <c r="D118" t="s">
+        <v>363</v>
+      </c>
+      <c r="E118" t="s">
+        <v>364</v>
+      </c>
+      <c r="F118" t="s">
+        <v>365</v>
+      </c>
+      <c r="G118" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>33967</v>
+        <v>66465</v>
       </c>
       <c r="B119">
-        <v>300869</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>519</v>
+        <v>300923</v>
+      </c>
+      <c r="C119" t="s">
+        <v>366</v>
+      </c>
+      <c r="D119" t="s">
+        <v>363</v>
+      </c>
+      <c r="E119" t="s">
+        <v>364</v>
+      </c>
+      <c r="F119" t="s">
+        <v>365</v>
+      </c>
+      <c r="G119" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>45838</v>
+        <v>66466</v>
       </c>
       <c r="B120">
-        <v>300871</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>520</v>
+        <v>300923</v>
+      </c>
+      <c r="C120" t="s">
+        <v>367</v>
+      </c>
+      <c r="D120" t="s">
+        <v>363</v>
+      </c>
+      <c r="E120" t="s">
+        <v>364</v>
+      </c>
+      <c r="F120" t="s">
+        <v>365</v>
+      </c>
+      <c r="G120" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>45839</v>
+        <v>84335</v>
       </c>
       <c r="B121">
-        <v>300871</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>520</v>
+        <v>143453</v>
+      </c>
+      <c r="C121" t="s">
+        <v>31</v>
+      </c>
+      <c r="D121" t="s">
+        <v>32</v>
+      </c>
+      <c r="E121" t="s">
+        <v>33</v>
+      </c>
+      <c r="F121" t="s">
+        <v>34</v>
+      </c>
+      <c r="G121" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4915,89 +4919,89 @@
       <c r="B122">
         <v>300906</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" t="s">
         <v>358</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" t="s">
         <v>359</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" t="s">
         <v>360</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" t="s">
         <v>361</v>
       </c>
-      <c r="G122" s="1">
+      <c r="G122">
         <v>135773</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>66464</v>
+        <v>84343</v>
       </c>
       <c r="B123">
-        <v>300923</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>521</v>
+        <v>143453</v>
+      </c>
+      <c r="C123" t="s">
+        <v>35</v>
+      </c>
+      <c r="D123" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" t="s">
+        <v>33</v>
+      </c>
+      <c r="F123" t="s">
+        <v>34</v>
+      </c>
+      <c r="G123" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>66465</v>
+        <v>23333</v>
       </c>
       <c r="B124">
-        <v>300923</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>521</v>
+        <v>300959</v>
+      </c>
+      <c r="C124" t="s">
+        <v>372</v>
+      </c>
+      <c r="D124" t="s">
+        <v>373</v>
+      </c>
+      <c r="E124" t="s">
+        <v>374</v>
+      </c>
+      <c r="F124" t="s">
+        <v>375</v>
+      </c>
+      <c r="G124" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>66466</v>
+        <v>23335</v>
       </c>
       <c r="B125">
-        <v>300923</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>521</v>
+        <v>300959</v>
+      </c>
+      <c r="C125" t="s">
+        <v>376</v>
+      </c>
+      <c r="D125" t="s">
+        <v>377</v>
+      </c>
+      <c r="E125" t="s">
+        <v>374</v>
+      </c>
+      <c r="F125" t="s">
+        <v>375</v>
+      </c>
+      <c r="G125" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5007,181 +5011,181 @@
       <c r="B126">
         <v>300953</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" t="s">
         <v>368</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" t="s">
         <v>369</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E126" t="s">
         <v>370</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" t="s">
         <v>371</v>
       </c>
-      <c r="G126" s="1">
+      <c r="G126">
         <v>143581</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>23333</v>
+        <v>23336</v>
       </c>
       <c r="B127">
         <v>300959</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="C127" t="s">
+        <v>378</v>
+      </c>
+      <c r="D127" t="s">
+        <v>377</v>
+      </c>
+      <c r="E127" t="s">
         <v>374</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" t="s">
         <v>375</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="G127" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>23335</v>
+        <v>85668</v>
       </c>
       <c r="B128">
-        <v>300959</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E128" s="1" t="s">
+        <v>300961</v>
+      </c>
+      <c r="C128" t="s">
+        <v>379</v>
+      </c>
+      <c r="D128" t="s">
+        <v>380</v>
+      </c>
+      <c r="E128" t="s">
         <v>374</v>
       </c>
-      <c r="F128" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>522</v>
+      <c r="F128" t="s">
+        <v>381</v>
+      </c>
+      <c r="G128" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>23336</v>
+        <v>23107</v>
       </c>
       <c r="B129">
-        <v>300959</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>522</v>
+        <v>300966</v>
+      </c>
+      <c r="C129" t="s">
+        <v>382</v>
+      </c>
+      <c r="D129" t="s">
+        <v>383</v>
+      </c>
+      <c r="E129" t="s">
+        <v>384</v>
+      </c>
+      <c r="F129" t="s">
+        <v>385</v>
+      </c>
+      <c r="G129" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>85668</v>
+        <v>23114</v>
       </c>
       <c r="B130">
-        <v>300961</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>523</v>
+        <v>300966</v>
+      </c>
+      <c r="C130" t="s">
+        <v>386</v>
+      </c>
+      <c r="D130" t="s">
+        <v>387</v>
+      </c>
+      <c r="E130" t="s">
+        <v>384</v>
+      </c>
+      <c r="F130" t="s">
+        <v>385</v>
+      </c>
+      <c r="G130" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>23107</v>
+        <v>23175</v>
       </c>
       <c r="B131">
-        <v>300966</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>524</v>
+        <v>300997</v>
+      </c>
+      <c r="C131" t="s">
+        <v>396</v>
+      </c>
+      <c r="D131" t="s">
+        <v>397</v>
+      </c>
+      <c r="E131" t="s">
+        <v>398</v>
+      </c>
+      <c r="F131" t="s">
+        <v>399</v>
+      </c>
+      <c r="G131" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>23114</v>
+        <v>85867</v>
       </c>
       <c r="B132">
-        <v>300966</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>524</v>
+        <v>301005</v>
+      </c>
+      <c r="C132" t="s">
+        <v>400</v>
+      </c>
+      <c r="D132" t="s">
+        <v>401</v>
+      </c>
+      <c r="E132" t="s">
+        <v>402</v>
+      </c>
+      <c r="F132" t="s">
+        <v>403</v>
+      </c>
+      <c r="G132" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>22723</v>
+        <v>46345</v>
       </c>
       <c r="B133">
-        <v>300974</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>525</v>
+        <v>301081</v>
+      </c>
+      <c r="C133" t="s">
+        <v>404</v>
+      </c>
+      <c r="D133" t="s">
+        <v>405</v>
+      </c>
+      <c r="E133" t="s">
+        <v>406</v>
+      </c>
+      <c r="F133" t="s">
+        <v>407</v>
+      </c>
+      <c r="G133" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5191,158 +5195,158 @@
       <c r="B134">
         <v>300989</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" t="s">
         <v>392</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" t="s">
         <v>393</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E134" t="s">
         <v>394</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" t="s">
         <v>395</v>
       </c>
-      <c r="G134" s="1">
+      <c r="G134">
         <v>147368</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>23175</v>
+        <v>69191</v>
       </c>
       <c r="B135">
-        <v>300997</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>526</v>
+        <v>301175</v>
+      </c>
+      <c r="C135" t="s">
+        <v>408</v>
+      </c>
+      <c r="D135" t="s">
+        <v>409</v>
+      </c>
+      <c r="E135" t="s">
+        <v>410</v>
+      </c>
+      <c r="F135" t="s">
+        <v>411</v>
+      </c>
+      <c r="G135" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>85867</v>
+        <v>69216</v>
       </c>
       <c r="B136">
-        <v>301005</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>527</v>
+        <v>301182</v>
+      </c>
+      <c r="C136" t="s">
+        <v>412</v>
+      </c>
+      <c r="D136" t="s">
+        <v>413</v>
+      </c>
+      <c r="E136" t="s">
+        <v>414</v>
+      </c>
+      <c r="F136" t="s">
+        <v>415</v>
+      </c>
+      <c r="G136" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>46345</v>
+        <v>61451</v>
       </c>
       <c r="B137">
-        <v>301081</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>528</v>
+        <v>301184</v>
+      </c>
+      <c r="C137" t="s">
+        <v>416</v>
+      </c>
+      <c r="D137" t="s">
+        <v>417</v>
+      </c>
+      <c r="E137" t="s">
+        <v>418</v>
+      </c>
+      <c r="F137" t="s">
+        <v>419</v>
+      </c>
+      <c r="G137" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>69191</v>
+        <v>7097</v>
       </c>
       <c r="B138">
-        <v>301175</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>529</v>
+        <v>301282</v>
+      </c>
+      <c r="C138" t="s">
+        <v>428</v>
+      </c>
+      <c r="D138" t="s">
+        <v>429</v>
+      </c>
+      <c r="E138" t="s">
+        <v>430</v>
+      </c>
+      <c r="F138" t="s">
+        <v>431</v>
+      </c>
+      <c r="G138" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>69216</v>
+        <v>73410</v>
       </c>
       <c r="B139">
-        <v>301182</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>530</v>
+        <v>301282</v>
+      </c>
+      <c r="C139" t="s">
+        <v>432</v>
+      </c>
+      <c r="D139" t="s">
+        <v>433</v>
+      </c>
+      <c r="E139" t="s">
+        <v>430</v>
+      </c>
+      <c r="F139" t="s">
+        <v>431</v>
+      </c>
+      <c r="G139" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>61451</v>
+        <v>78049</v>
       </c>
       <c r="B140">
-        <v>301184</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>531</v>
+        <v>301288</v>
+      </c>
+      <c r="C140" t="s">
+        <v>434</v>
+      </c>
+      <c r="D140" t="s">
+        <v>435</v>
+      </c>
+      <c r="E140" t="s">
+        <v>436</v>
+      </c>
+      <c r="F140" t="s">
+        <v>437</v>
+      </c>
+      <c r="G140" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -5352,19 +5356,19 @@
       <c r="B141">
         <v>301214</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" t="s">
         <v>420</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" t="s">
         <v>421</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E141" t="s">
         <v>422</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F141" t="s">
         <v>423</v>
       </c>
-      <c r="G141" s="1">
+      <c r="G141">
         <v>185766</v>
       </c>
     </row>
@@ -5375,181 +5379,181 @@
       <c r="B142">
         <v>301221</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" t="s">
         <v>424</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" t="s">
         <v>425</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="E142" t="s">
         <v>426</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" t="s">
         <v>427</v>
       </c>
-      <c r="G142" s="1">
+      <c r="G142">
         <v>186253</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>7097</v>
+        <v>77893</v>
       </c>
       <c r="B143">
-        <v>301282</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>532</v>
+        <v>301289</v>
+      </c>
+      <c r="C143" t="s">
+        <v>438</v>
+      </c>
+      <c r="D143" t="s">
+        <v>439</v>
+      </c>
+      <c r="E143" t="s">
+        <v>440</v>
+      </c>
+      <c r="F143" t="s">
+        <v>441</v>
+      </c>
+      <c r="G143" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>73410</v>
+        <v>77894</v>
       </c>
       <c r="B144">
-        <v>301282</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>532</v>
+        <v>301289</v>
+      </c>
+      <c r="C144" t="s">
+        <v>442</v>
+      </c>
+      <c r="D144" t="s">
+        <v>439</v>
+      </c>
+      <c r="E144" t="s">
+        <v>440</v>
+      </c>
+      <c r="F144" t="s">
+        <v>441</v>
+      </c>
+      <c r="G144" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>78049</v>
+        <v>77919</v>
       </c>
       <c r="B145">
-        <v>301288</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>533</v>
+        <v>301289</v>
+      </c>
+      <c r="C145" t="s">
+        <v>443</v>
+      </c>
+      <c r="D145" t="s">
+        <v>444</v>
+      </c>
+      <c r="E145" t="s">
+        <v>440</v>
+      </c>
+      <c r="F145" t="s">
+        <v>441</v>
+      </c>
+      <c r="G145" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>77893</v>
+        <v>41185</v>
       </c>
       <c r="B146">
-        <v>301289</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>534</v>
+        <v>301292</v>
+      </c>
+      <c r="C146" t="s">
+        <v>445</v>
+      </c>
+      <c r="D146" t="s">
+        <v>446</v>
+      </c>
+      <c r="E146" t="s">
+        <v>447</v>
+      </c>
+      <c r="F146" t="s">
+        <v>448</v>
+      </c>
+      <c r="G146" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>77894</v>
+        <v>41246</v>
       </c>
       <c r="B147">
-        <v>301289</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>534</v>
+        <v>200935</v>
+      </c>
+      <c r="C147" t="s">
+        <v>44</v>
+      </c>
+      <c r="D147" t="s">
+        <v>45</v>
+      </c>
+      <c r="E147" t="s">
+        <v>46</v>
+      </c>
+      <c r="F147" t="s">
+        <v>47</v>
+      </c>
+      <c r="G147" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>77919</v>
+        <v>45162</v>
       </c>
       <c r="B148">
-        <v>301289</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>534</v>
+        <v>202861</v>
+      </c>
+      <c r="C148" t="s">
+        <v>48</v>
+      </c>
+      <c r="D148" t="s">
+        <v>49</v>
+      </c>
+      <c r="E148" t="s">
+        <v>50</v>
+      </c>
+      <c r="F148" t="s">
+        <v>51</v>
+      </c>
+      <c r="G148" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>41185</v>
+        <v>22723</v>
       </c>
       <c r="B149">
-        <v>301292</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>535</v>
+        <v>300974</v>
+      </c>
+      <c r="C149" t="s">
+        <v>388</v>
+      </c>
+      <c r="D149" t="s">
+        <v>389</v>
+      </c>
+      <c r="E149" t="s">
+        <v>390</v>
+      </c>
+      <c r="F149" t="s">
+        <v>391</v>
+      </c>
+      <c r="G149" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -5559,19 +5563,19 @@
       <c r="B150">
         <v>301299</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" t="s">
         <v>449</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="D150" t="s">
         <v>450</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="E150" t="s">
         <v>451</v>
       </c>
-      <c r="F150" s="1" t="s">
+      <c r="F150" t="s">
         <v>452</v>
       </c>
-      <c r="G150" s="1">
+      <c r="G150">
         <v>200571</v>
       </c>
     </row>
@@ -5582,19 +5586,19 @@
       <c r="B151">
         <v>301310</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" t="s">
         <v>453</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D151" t="s">
         <v>454</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E151" t="s">
         <v>455</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F151" t="s">
         <v>456</v>
       </c>
-      <c r="G151" s="1">
+      <c r="G151">
         <v>202226</v>
       </c>
     </row>
@@ -5624,10 +5628,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>321844</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>119573</v>
       </c>
     </row>
@@ -5635,7 +5639,7 @@
       <c r="A3">
         <v>325929</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>143453</v>
       </c>
     </row>
@@ -5643,7 +5647,7 @@
       <c r="A4">
         <v>336477</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>200935</v>
       </c>
     </row>
